--- a/Data Files/1.1. Send Proxy Alias to get One Proxy list.xlsx
+++ b/Data Files/1.1. Send Proxy Alias to get One Proxy list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chindy\Chindy\BIFAST\Revamp\Automation\Komi-API BIFAST 2.0\Komi-API Now\Komi-API\Data Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wirafidi/git/Bifast-2.0-Katalon/Data Files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535D04CF-32DE-4E7E-B12A-6267F9D273F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A2F1BF-EB76-7E4B-A98E-79B27C3FB48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BE19A422-6A00-48DE-86CA-72B8BA794C08}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="23260" windowHeight="12460" xr2:uid="{BE19A422-6A00-48DE-86CA-72B8BA794C08}"/>
   </bookViews>
   <sheets>
     <sheet name="PROXY" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Content_Type</t>
   </si>
@@ -36,21 +36,12 @@
     <t>transactionCode</t>
   </si>
   <si>
-    <t>cid</t>
-  </si>
-  <si>
     <t>channelType</t>
   </si>
   <si>
     <t>application/json</t>
   </si>
   <si>
-    <t>FAST-JSON-MBL-03</t>
-  </si>
-  <si>
-    <t>MBL</t>
-  </si>
-  <si>
     <t>proxyAlias</t>
   </si>
   <si>
@@ -63,13 +54,25 @@
     <t>11UNBU</t>
   </si>
   <si>
-    <t>0019845621101</t>
-  </si>
-  <si>
-    <t>08213528061</t>
-  </si>
-  <si>
-    <t>250821104239</t>
+    <t>institutionBic</t>
+  </si>
+  <si>
+    <t>200000</t>
+  </si>
+  <si>
+    <t>250821104234</t>
+  </si>
+  <si>
+    <t>BMRIIDJA</t>
+  </si>
+  <si>
+    <t>08833223322</t>
+  </si>
+  <si>
+    <t>0066721469312</t>
+  </si>
+  <si>
+    <t>KOMIMOBILE</t>
   </si>
 </sst>
 </file>
@@ -135,7 +138,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -146,9 +149,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -168,9 +168,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -208,7 +208,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -314,7 +314,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -456,7 +456,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -465,61 +465,61 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EAC831-256C-49B0-B0F6-AAF164E4E88A}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="8" width="20.21875" customWidth="1"/>
+    <col min="1" max="8" width="20.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="6">
-        <v>230000</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>6</v>
-      </c>
       <c r="H2" s="3" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
